--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -908,7 +908,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
         <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>-37.5</v>
+        <v>-62.5</v>
       </c>
       <c r="I16" s="15">
         <v>9</v>
       </c>
       <c r="J16" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K16" s="14">
-        <v>-30.769230769230</v>
+        <v>-40</v>
       </c>
       <c r="L16" s="14">
-        <v>28.571428571428</v>
+        <v>-10</v>
       </c>
       <c r="M16" s="14">
-        <v>-60.869565217391</v>
+        <v>-62.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.909090909090</v>
+        <v>-91.743119266055</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
         <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H17" s="14">
-        <v>-5.555555555555</v>
+        <v>-18.75</v>
       </c>
       <c r="I17" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J17" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K17" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M17" s="14">
-        <v>162.5</v>
+        <v>144.444444444444</v>
       </c>
       <c r="N17" s="14">
-        <v>162.5</v>
+        <v>83.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
         <v>21</v>
       </c>
       <c r="H18" s="14">
-        <v>-76.190476190476</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="I18" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J18" s="15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K18" s="14">
-        <v>-77.777777777777</v>
+        <v>-71.875</v>
       </c>
       <c r="L18" s="14">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="M18" s="14">
-        <v>-53.846153846153</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.319018404908</v>
+        <v>-95.5</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,81 +1060,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>7</v>
+      </c>
+      <c r="D19" s="15">
         <v>5</v>
       </c>
-      <c r="D19" s="15">
-        <v>9</v>
-      </c>
       <c r="E19" s="14">
-        <v>-44.444444444444</v>
+        <v>40</v>
       </c>
       <c r="F19" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G19" s="15">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>10.344827586206</v>
       </c>
       <c r="I19" s="15">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="J19" s="15">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K19" s="14">
-        <v>6.976744186046</v>
+        <v>12.5</v>
       </c>
       <c r="L19" s="14">
-        <v>24.324324324324</v>
+        <v>22.727272727272</v>
       </c>
       <c r="M19" s="14">
-        <v>-11.538461538461</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="N19" s="14">
-        <v>-48.888888888888</v>
+        <v>-50.458715596330</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>4</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J20" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20" s="14">
-        <v>-25</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L20" s="14">
         <v>33.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.339246119733</v>
+        <v>-96.862745098039</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.529411764705</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F21" s="17">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.089887640449</v>
+        <v>-23.170731707317</v>
       </c>
       <c r="I21" s="17">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="J21" s="17">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.008403361344</v>
+        <v>-19.708029197080</v>
       </c>
       <c r="L21" s="18">
-        <v>27.027027027027</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.071428571428</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-88.437884378843</v>
+        <v>-88.322717622080</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
         <v>-100</v>
@@ -1204,16 +1204,16 @@
         <v>2</v>
       </c>
       <c r="J22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
         <v>49</v>
       </c>
       <c r="E24" s="14">
-        <v>-36.734693877551</v>
+        <v>-48.979591836734</v>
       </c>
       <c r="F24" s="15">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="G24" s="15">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H24" s="14">
-        <v>-11.180124223602</v>
+        <v>-27.218934911242</v>
       </c>
       <c r="I24" s="15">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="J24" s="15">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="K24" s="14">
-        <v>0.938967136150</v>
+        <v>-8.778625954198</v>
       </c>
       <c r="L24" s="14">
-        <v>28.742514970059</v>
+        <v>18.905472636815</v>
       </c>
       <c r="M24" s="14">
-        <v>150</v>
+        <v>156.989247311828</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D25" s="15">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E25" s="14">
-        <v>-43.589743589743</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="15">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="G25" s="15">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="H25" s="14">
-        <v>-17.910447761194</v>
+        <v>-32.191780821917</v>
       </c>
       <c r="I25" s="15">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="J25" s="15">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="K25" s="14">
-        <v>-18.079096045197</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="L25" s="14">
-        <v>16</v>
+        <v>2.531645569620</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>-63.636363636363</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F26" s="15">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G26" s="15">
         <v>33</v>
       </c>
       <c r="H26" s="14">
-        <v>-18.181818181818</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="I26" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J26" s="15">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K26" s="14">
-        <v>-2.702702702702</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L26" s="14">
-        <v>89.473684210526</v>
+        <v>81.818181818181</v>
       </c>
       <c r="M26" s="14">
-        <v>38.461538461538</v>
+        <v>29.032258064516</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1409,7 +1409,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="14">
         <v>-100</v>
@@ -1447,16 +1447,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="14">
         <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>3</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="15">
-        <v>2</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G31" s="15">
+        <v>3</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-66.666666666666</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="15">
+        <v>3</v>
+      </c>
+      <c r="K31" s="14">
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
@@ -1610,8 +1610,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="15">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -907,11 +907,11 @@
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>20</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-62.5</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I16" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J16" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K16" s="14">
-        <v>-40</v>
+        <v>-18.75</v>
       </c>
       <c r="L16" s="14">
-        <v>-10</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M16" s="14">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.743119266055</v>
+        <v>-89.256198347107</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-75</v>
+        <v>150</v>
       </c>
       <c r="F17" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>-18.75</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J17" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="L17" s="14">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M17" s="14">
-        <v>144.444444444444</v>
+        <v>200</v>
       </c>
       <c r="N17" s="14">
-        <v>83.333333333333</v>
+        <v>92.857142857142</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-60</v>
+        <v>200</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-61.904761904761</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I18" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J18" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" s="14">
-        <v>-71.875</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L18" s="14">
-        <v>-25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M18" s="14">
-        <v>-35.714285714285</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N18" s="14">
-        <v>-95.5</v>
+        <v>-94.805194805194</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>40</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F19" s="15">
         <v>32</v>
       </c>
       <c r="G19" s="15">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H19" s="14">
-        <v>10.344827586206</v>
+        <v>3.225806451612</v>
       </c>
       <c r="I19" s="15">
+        <v>67</v>
+      </c>
+      <c r="J19" s="15">
         <v>54</v>
       </c>
-      <c r="J19" s="15">
-        <v>48</v>
-      </c>
       <c r="K19" s="14">
-        <v>12.5</v>
+        <v>24.074074074074</v>
       </c>
       <c r="L19" s="14">
-        <v>22.727272727272</v>
+        <v>31.372549019607</v>
       </c>
       <c r="M19" s="14">
-        <v>-5.263157894736</v>
+        <v>9.836065573770</v>
       </c>
       <c r="N19" s="14">
-        <v>-50.458715596330</v>
+        <v>-49.242424242424</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1113,28 +1113,28 @@
         <v>7</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I20" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J20" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K20" s="14">
-        <v>-11.111111111111</v>
+        <v>-5</v>
       </c>
       <c r="L20" s="14">
-        <v>33.333333333333</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M20" s="14">
         <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.862745098039</v>
+        <v>-96.729776247848</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,78 +1142,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.222222222222</v>
+        <v>141.666666666667</v>
       </c>
       <c r="F21" s="17">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G21" s="17">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.170731707317</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="I21" s="17">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="J21" s="17">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.708029197080</v>
+        <v>-7.382550335570</v>
       </c>
       <c r="L21" s="18">
-        <v>22.222222222222</v>
+        <v>33.980582524271</v>
       </c>
       <c r="M21" s="18">
-        <v>-8.333333333333</v>
+        <v>3.759398496240</v>
       </c>
       <c r="N21" s="18">
-        <v>-88.322717622080</v>
+        <v>-87.234042553191</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="15">
         <v>1</v>
       </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="15">
         <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="15">
         <v>6</v>
       </c>
       <c r="K22" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M22" s="14">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D24" s="15">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E24" s="14">
-        <v>-48.979591836734</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="F24" s="15">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G24" s="15">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="H24" s="14">
-        <v>-27.218934911242</v>
+        <v>-31.693989071038</v>
       </c>
       <c r="I24" s="15">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="J24" s="15">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="K24" s="14">
-        <v>-8.778625954198</v>
+        <v>-10.509554140127</v>
       </c>
       <c r="L24" s="14">
-        <v>18.905472636815</v>
+        <v>19.067796610169</v>
       </c>
       <c r="M24" s="14">
-        <v>156.989247311828</v>
+        <v>167.619047619048</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D25" s="15">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E25" s="14">
-        <v>-60</v>
+        <v>-2.5</v>
       </c>
       <c r="F25" s="15">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="G25" s="15">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H25" s="14">
-        <v>-32.191780821917</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="I25" s="15">
-        <v>162</v>
+        <v>201</v>
       </c>
       <c r="J25" s="15">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="K25" s="14">
-        <v>-27.027027027027</v>
+        <v>-23.282442748091</v>
       </c>
       <c r="L25" s="14">
-        <v>2.531645569620</v>
+        <v>7.486631016042</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>-55.555555555555</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G26" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H26" s="14">
-        <v>-30.303030303030</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="I26" s="15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J26" s="15">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K26" s="14">
-        <v>-13.043478260869</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="L26" s="14">
-        <v>81.818181818181</v>
+        <v>41.935483870967</v>
       </c>
       <c r="M26" s="14">
-        <v>29.032258064516</v>
+        <v>29.411764705882</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,17 +1390,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="15">
-        <v>3</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1438,25 +1438,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
         <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>3</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
-      </c>
-      <c r="D16" s="15">
         <v>1</v>
       </c>
-      <c r="E16" s="14">
-        <v>300</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H16" s="14">
-        <v>-14.285714285714</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J16" s="15">
         <v>16</v>
       </c>
       <c r="K16" s="14">
-        <v>-18.75</v>
+        <v>-6.25</v>
       </c>
       <c r="L16" s="14">
-        <v>18.181818181818</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M16" s="14">
-        <v>-50</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.256198347107</v>
+        <v>-88.970588235294</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>-6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J17" s="15">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K17" s="14">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="L17" s="14">
-        <v>125</v>
+        <v>141.666666666667</v>
       </c>
       <c r="M17" s="14">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="N17" s="14">
-        <v>92.857142857142</v>
+        <v>107.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>200</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="15">
         <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-21.428571428571</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K18" s="14">
-        <v>-63.636363636363</v>
+        <v>-64.864864864864</v>
       </c>
       <c r="L18" s="14">
-        <v>-14.285714285714</v>
+        <v>-18.75</v>
       </c>
       <c r="M18" s="14">
-        <v>-33.333333333333</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.805194805194</v>
+        <v>-94.881889763779</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
         <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>116.666666666667</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="15">
         <v>32</v>
       </c>
       <c r="G19" s="15">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="H19" s="14">
-        <v>3.225806451612</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I19" s="15">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="J19" s="15">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K19" s="14">
-        <v>24.074074074074</v>
+        <v>23.333333333333</v>
       </c>
       <c r="L19" s="14">
-        <v>31.372549019607</v>
+        <v>19.354838709677</v>
       </c>
       <c r="M19" s="14">
-        <v>9.836065573770</v>
+        <v>13.846153846153</v>
       </c>
       <c r="N19" s="14">
-        <v>-49.242424242424</v>
+        <v>-51.948051948051</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
+        <v>9</v>
+      </c>
+      <c r="G20" s="15">
         <v>7</v>
       </c>
-      <c r="G20" s="15">
-        <v>9</v>
-      </c>
       <c r="H20" s="14">
-        <v>-22.222222222222</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I20" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J20" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K20" s="14">
-        <v>-5</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="L20" s="14">
-        <v>35.714285714285</v>
+        <v>5</v>
       </c>
       <c r="M20" s="14">
         <v>0</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.729776247848</v>
+        <v>-96.623794212218</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>141.666666666667</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
         <v>70</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.894736842105</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="J21" s="17">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.382550335570</v>
+        <v>-6.172839506172</v>
       </c>
       <c r="L21" s="18">
-        <v>33.980582524271</v>
+        <v>24.590163934426</v>
       </c>
       <c r="M21" s="18">
-        <v>3.759398496240</v>
+        <v>4.827586206896</v>
       </c>
       <c r="N21" s="18">
-        <v>-87.234042553191</v>
+        <v>-87.140439932318</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1210,10 +1210,10 @@
         <v>-50</v>
       </c>
       <c r="L22" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="M22" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D24" s="15">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E24" s="14">
-        <v>-19.230769230769</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="F24" s="15">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G24" s="15">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="H24" s="14">
-        <v>-31.693989071038</v>
+        <v>-36.410256410256</v>
       </c>
       <c r="I24" s="15">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="J24" s="15">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="K24" s="14">
-        <v>-10.509554140127</v>
+        <v>-14.484679665738</v>
       </c>
       <c r="L24" s="14">
-        <v>19.067796610169</v>
+        <v>6.597222222222</v>
       </c>
       <c r="M24" s="14">
-        <v>167.619047619048</v>
+        <v>155.833333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D25" s="15">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E25" s="14">
-        <v>-2.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F25" s="15">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G25" s="15">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H25" s="14">
-        <v>-32.258064516129</v>
+        <v>-39.375</v>
       </c>
       <c r="I25" s="15">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="J25" s="15">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="K25" s="14">
-        <v>-23.282442748091</v>
+        <v>-26.174496644295</v>
       </c>
       <c r="L25" s="14">
-        <v>7.486631016042</v>
+        <v>-3.083700440528</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="F26" s="15">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G26" s="15">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H26" s="14">
-        <v>-38.235294117647</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="I26" s="15">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J26" s="15">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K26" s="14">
-        <v>-10.204081632653</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L26" s="14">
-        <v>41.935483870967</v>
+        <v>24.390243902439</v>
       </c>
       <c r="M26" s="14">
-        <v>29.411764705882</v>
+        <v>15.909090909090</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1438,25 +1438,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="14">
         <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,32 +1554,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="15">
-        <v>1</v>
+      <c r="D31" s="15">
+        <v>2</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H31" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K31" s="14">
-        <v>0</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>-40</v>
+      </c>
+      <c r="L31" s="14">
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,8 +904,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="15">
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -913,64 +913,64 @@
       <c r="H15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
+      <c r="I15" s="15">
+        <v>2</v>
       </c>
       <c r="J15" s="15">
         <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H16" s="14">
-        <v>133.333333333333</v>
+        <v>20</v>
       </c>
       <c r="I16" s="15">
         <v>15</v>
       </c>
       <c r="J16" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16" s="14">
-        <v>-6.25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>36.363636363636</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M16" s="14">
         <v>-46.428571428571</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.970588235294</v>
+        <v>-89.795918367346</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>-80</v>
       </c>
       <c r="F17" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
+        <v>-25</v>
+      </c>
+      <c r="I17" s="15">
+        <v>30</v>
+      </c>
+      <c r="J17" s="15">
+        <v>30</v>
+      </c>
+      <c r="K17" s="14">
         <v>0</v>
       </c>
-      <c r="I17" s="15">
-        <v>29</v>
-      </c>
-      <c r="J17" s="15">
-        <v>25</v>
-      </c>
-      <c r="K17" s="14">
-        <v>16</v>
-      </c>
       <c r="L17" s="14">
-        <v>141.666666666667</v>
+        <v>114.285714285714</v>
       </c>
       <c r="M17" s="14">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="N17" s="14">
-        <v>107.142857142857</v>
+        <v>114.285714285714</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G18" s="15">
         <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-15.384615384615</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J18" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K18" s="14">
-        <v>-64.864864864864</v>
+        <v>-60</v>
       </c>
       <c r="L18" s="14">
-        <v>-18.75</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M18" s="14">
-        <v>-38.095238095238</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.881889763779</v>
+        <v>-94.346289752650</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15">
         <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>16.666666666666</v>
+        <v>150</v>
       </c>
       <c r="F19" s="15">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G19" s="15">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H19" s="14">
-        <v>23.076923076923</v>
+        <v>86.956521739130</v>
       </c>
       <c r="I19" s="15">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J19" s="15">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K19" s="14">
-        <v>23.333333333333</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L19" s="14">
-        <v>19.354838709677</v>
+        <v>34.328358208955</v>
       </c>
       <c r="M19" s="14">
-        <v>13.846153846153</v>
+        <v>25</v>
       </c>
       <c r="N19" s="14">
-        <v>-51.948051948051</v>
+        <v>-48.571428571428</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
       </c>
       <c r="E20" s="14">
+        <v>100</v>
+      </c>
+      <c r="F20" s="15">
+        <v>13</v>
+      </c>
+      <c r="G20" s="15">
+        <v>8</v>
+      </c>
+      <c r="H20" s="14">
+        <v>62.5</v>
+      </c>
+      <c r="I20" s="15">
+        <v>25</v>
+      </c>
+      <c r="J20" s="15">
+        <v>24</v>
+      </c>
+      <c r="K20" s="14">
+        <v>4.166666666666</v>
+      </c>
+      <c r="L20" s="14">
         <v>0</v>
       </c>
-      <c r="F20" s="15">
-        <v>9</v>
-      </c>
-      <c r="G20" s="15">
-        <v>7</v>
-      </c>
-      <c r="H20" s="14">
-        <v>28.571428571428</v>
-      </c>
-      <c r="I20" s="15">
-        <v>21</v>
-      </c>
-      <c r="J20" s="15">
-        <v>22</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-4.545454545454</v>
-      </c>
-      <c r="L20" s="14">
-        <v>5</v>
-      </c>
       <c r="M20" s="14">
-        <v>0</v>
+        <v>8.695652173913</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.623794212218</v>
+        <v>-96.234939759036</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H21" s="18">
-        <v>16.666666666666</v>
+        <v>34.426229508196</v>
       </c>
       <c r="I21" s="17">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="J21" s="17">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.172839506172</v>
+        <v>-1.111111111111</v>
       </c>
       <c r="L21" s="18">
-        <v>24.590163934426</v>
+        <v>28.057553956834</v>
       </c>
       <c r="M21" s="18">
-        <v>4.827586206896</v>
+        <v>14.102564102564</v>
       </c>
       <c r="N21" s="18">
-        <v>-87.140439932318</v>
+        <v>-86.147859922179</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,35 +1185,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>2</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
         <v>3</v>
       </c>
       <c r="J22" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="14">
+        <v>-62.5</v>
+      </c>
+      <c r="L22" s="14">
+        <v>-62.5</v>
+      </c>
+      <c r="M22" s="14">
         <v>-50</v>
-      </c>
-      <c r="L22" s="14">
-        <v>-40</v>
-      </c>
-      <c r="M22" s="14">
-        <v>-40</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D24" s="15">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E24" s="14">
-        <v>-37.777777777777</v>
+        <v>43.243243243243</v>
       </c>
       <c r="F24" s="15">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="G24" s="15">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="H24" s="14">
-        <v>-36.410256410256</v>
+        <v>-21.311475409836</v>
       </c>
       <c r="I24" s="15">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="J24" s="15">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="K24" s="14">
-        <v>-14.484679665738</v>
+        <v>-9.848484848484</v>
       </c>
       <c r="L24" s="14">
-        <v>6.597222222222</v>
+        <v>12.618296529968</v>
       </c>
       <c r="M24" s="14">
-        <v>155.833333333333</v>
+        <v>125.949367088608</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D25" s="15">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E25" s="14">
-        <v>-44.444444444444</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F25" s="15">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G25" s="15">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="H25" s="14">
-        <v>-39.375</v>
+        <v>-34.193548387096</v>
       </c>
       <c r="I25" s="15">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="J25" s="15">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="K25" s="14">
-        <v>-26.174496644295</v>
+        <v>-25.903614457831</v>
       </c>
       <c r="L25" s="14">
-        <v>-3.083700440528</v>
+        <v>-1.992031872509</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E26" s="14">
-        <v>40</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="15">
         <v>19</v>
       </c>
       <c r="G26" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>-32.142857142857</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="I26" s="15">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J26" s="15">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="K26" s="14">
-        <v>-5.555555555555</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L26" s="14">
-        <v>24.390243902439</v>
+        <v>25</v>
       </c>
       <c r="M26" s="14">
-        <v>15.909090909090</v>
+        <v>22.222222222222</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>2</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>100</v>
+      </c>
+      <c r="F27" s="15">
+        <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
+        <v>2</v>
       </c>
       <c r="J27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-100</v>
+        <v>-60</v>
       </c>
       <c r="L27" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1432,31 +1432,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="15">
         <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L28" s="14">
-        <v>133.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>2</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1619,8 +1619,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="15">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="I16" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" s="14">
-        <v>-16.666666666666</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L16" s="14">
-        <v>7.142857142857</v>
+        <v>6.25</v>
       </c>
       <c r="M16" s="14">
-        <v>-46.428571428571</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.795918367346</v>
+        <v>-88.961038961039</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>-80</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J17" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K17" s="14">
         <v>0</v>
       </c>
       <c r="L17" s="14">
-        <v>114.285714285714</v>
+        <v>94.117647058823</v>
       </c>
       <c r="M17" s="14">
         <v>200</v>
       </c>
       <c r="N17" s="14">
-        <v>114.285714285714</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-30.769230769230</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J18" s="15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K18" s="14">
-        <v>-60</v>
+        <v>-56.818181818181</v>
       </c>
       <c r="L18" s="14">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="M18" s="14">
-        <v>-30.434782608695</v>
+        <v>-24</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.346289752650</v>
+        <v>-93.624161073825</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E19" s="14">
-        <v>150</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="15">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G19" s="15">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H19" s="14">
-        <v>86.956521739130</v>
+        <v>44.117647058823</v>
       </c>
       <c r="I19" s="15">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="J19" s="15">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="K19" s="14">
-        <v>36.363636363636</v>
+        <v>25.609756097561</v>
       </c>
       <c r="L19" s="14">
-        <v>34.328358208955</v>
+        <v>35.526315789473</v>
       </c>
       <c r="M19" s="14">
-        <v>25</v>
+        <v>24.096385542168</v>
       </c>
       <c r="N19" s="14">
-        <v>-48.571428571428</v>
+        <v>-46.632124352331</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
+        <v>11</v>
+      </c>
+      <c r="G20" s="15">
+        <v>7</v>
+      </c>
+      <c r="H20" s="14">
+        <v>57.142857142857</v>
+      </c>
+      <c r="I20" s="15">
+        <v>26</v>
+      </c>
+      <c r="J20" s="15">
+        <v>25</v>
+      </c>
+      <c r="K20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
-      <c r="E20" s="14">
-        <v>100</v>
-      </c>
-      <c r="F20" s="15">
-        <v>13</v>
-      </c>
-      <c r="G20" s="15">
-        <v>8</v>
-      </c>
-      <c r="H20" s="14">
-        <v>62.5</v>
-      </c>
-      <c r="I20" s="15">
-        <v>25</v>
-      </c>
-      <c r="J20" s="15">
-        <v>24</v>
-      </c>
-      <c r="K20" s="14">
-        <v>4.166666666666</v>
-      </c>
       <c r="L20" s="14">
-        <v>0</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="M20" s="14">
-        <v>8.695652173913</v>
+        <v>8.333333333333</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.234939759036</v>
+        <v>-96.438356164383</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,78 +1142,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>34.426229508196</v>
+        <v>32.352941176470</v>
       </c>
       <c r="I21" s="17">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="J21" s="17">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.111111111111</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="L21" s="18">
-        <v>28.057553956834</v>
+        <v>27.388535031847</v>
       </c>
       <c r="M21" s="18">
-        <v>14.102564102564</v>
+        <v>16.279069767441</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.147859922179</v>
+        <v>-85.632183908046</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
         <v>2</v>
       </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="15">
-        <v>1</v>
-      </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="15">
         <v>8</v>
       </c>
       <c r="K22" s="14">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="14">
-        <v>-62.5</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M22" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D24" s="15">
         <v>37</v>
       </c>
       <c r="E24" s="14">
-        <v>43.243243243243</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="F24" s="15">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="G24" s="15">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="H24" s="14">
-        <v>-21.311475409836</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="I24" s="15">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="J24" s="15">
-        <v>396</v>
+        <v>433</v>
       </c>
       <c r="K24" s="14">
-        <v>-9.848484848484</v>
+        <v>-9.237875288683</v>
       </c>
       <c r="L24" s="14">
-        <v>12.618296529968</v>
+        <v>11.331444759206</v>
       </c>
       <c r="M24" s="14">
-        <v>125.949367088608</v>
+        <v>114.754098360656</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D25" s="15">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E25" s="14">
-        <v>-17.647058823529</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F25" s="15">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="G25" s="15">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="H25" s="14">
-        <v>-34.193548387096</v>
+        <v>-16.058394160583</v>
       </c>
       <c r="I25" s="15">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="J25" s="15">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="K25" s="14">
-        <v>-25.903614457831</v>
+        <v>-22.841225626740</v>
       </c>
       <c r="L25" s="14">
-        <v>-1.992031872509</v>
+        <v>-1.423487544483</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>-66.666666666666</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G26" s="15">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H26" s="14">
-        <v>-34.482758620689</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I26" s="15">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J26" s="15">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K26" s="14">
-        <v>-16.666666666666</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="L26" s="14">
-        <v>25</v>
+        <v>19.230769230769</v>
       </c>
       <c r="M26" s="14">
-        <v>22.222222222222</v>
+        <v>31.914893617021</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,23 +1387,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>2</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>100</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
@@ -1415,7 +1415,7 @@
         <v>-60</v>
       </c>
       <c r="L27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1431,32 +1431,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-50</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="15">
         <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,35 +1551,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
+      </c>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>0</v>
+      </c>
+      <c r="F31" s="15">
+        <v>1</v>
       </c>
       <c r="G31" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H31" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K31" s="14">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>75</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="15">
         <v>17</v>
       </c>
       <c r="J16" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K16" s="14">
-        <v>-10.526315789473</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="L16" s="14">
         <v>6.25</v>
       </c>
       <c r="M16" s="14">
-        <v>-41.379310344827</v>
+        <v>-45.161290322580</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.961038961039</v>
+        <v>-89.880952380952</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
         <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
         <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J17" s="15">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K17" s="14">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>94.117647058823</v>
+        <v>105.263157894737</v>
       </c>
       <c r="M17" s="14">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="N17" s="14">
-        <v>120</v>
+        <v>116.666666666667</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-16.666666666666</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I18" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="15">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K18" s="14">
-        <v>-56.818181818181</v>
+        <v>-55.319148936170</v>
       </c>
       <c r="L18" s="14">
         <v>0</v>
       </c>
       <c r="M18" s="14">
-        <v>-24</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.624161073825</v>
+        <v>-93.396226415094</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E19" s="14">
-        <v>-25</v>
+        <v>350</v>
       </c>
       <c r="F19" s="15">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G19" s="15">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H19" s="14">
-        <v>44.117647058823</v>
+        <v>50</v>
       </c>
       <c r="I19" s="15">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="J19" s="15">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K19" s="14">
-        <v>25.609756097561</v>
+        <v>34.523809523809</v>
       </c>
       <c r="L19" s="14">
-        <v>35.526315789473</v>
+        <v>29.885057471264</v>
       </c>
       <c r="M19" s="14">
-        <v>24.096385542168</v>
+        <v>18.947368421052</v>
       </c>
       <c r="N19" s="14">
-        <v>-46.632124352331</v>
+        <v>-46.190476190476</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="15">
         <v>11</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H20" s="14">
-        <v>57.142857142857</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J20" s="15">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K20" s="14">
-        <v>4</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="L20" s="14">
-        <v>-3.703703703703</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M20" s="14">
-        <v>8.333333333333</v>
+        <v>3.448275862068</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.438356164383</v>
+        <v>-96.163682864450</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1145,69 +1145,69 @@
         <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-20</v>
+        <v>17.647058823529</v>
       </c>
       <c r="F21" s="17">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>32.352941176470</v>
+        <v>12.328767123287</v>
       </c>
       <c r="I21" s="17">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="J21" s="17">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.439024390243</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>27.388535031847</v>
+        <v>24.022346368715</v>
       </c>
       <c r="M21" s="18">
-        <v>16.279069767441</v>
+        <v>13.265306122449</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.632183908046</v>
+        <v>-85.180240320427</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
         <v>4</v>
       </c>
       <c r="J22" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="14">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L22" s="14">
         <v>-55.555555555555</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D24" s="15">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E24" s="14">
-        <v>-2.702702702702</v>
+        <v>32</v>
       </c>
       <c r="F24" s="15">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G24" s="15">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="H24" s="14">
-        <v>-8.771929824561</v>
+        <v>2.777777777777</v>
       </c>
       <c r="I24" s="15">
-        <v>393</v>
+        <v>426</v>
       </c>
       <c r="J24" s="15">
-        <v>433</v>
+        <v>458</v>
       </c>
       <c r="K24" s="14">
-        <v>-9.237875288683</v>
+        <v>-6.986899563318</v>
       </c>
       <c r="L24" s="14">
-        <v>11.331444759206</v>
+        <v>11.811023622047</v>
       </c>
       <c r="M24" s="14">
-        <v>114.754098360656</v>
+        <v>107.80487804878</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D25" s="15">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E25" s="14">
-        <v>11.111111111111</v>
+        <v>15.789473684210</v>
       </c>
       <c r="F25" s="15">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="G25" s="15">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="H25" s="14">
-        <v>-16.058394160583</v>
+        <v>-14.655172413793</v>
       </c>
       <c r="I25" s="15">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="J25" s="15">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="K25" s="14">
-        <v>-22.841225626740</v>
+        <v>-20.899470899470</v>
       </c>
       <c r="L25" s="14">
-        <v>-1.423487544483</v>
+        <v>-1.644736842105</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1356,28 +1356,28 @@
         <v>-12.5</v>
       </c>
       <c r="F26" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G26" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H26" s="14">
-        <v>-21.428571428571</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="I26" s="15">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J26" s="15">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K26" s="14">
-        <v>-16.216216216216</v>
+        <v>-15.853658536585</v>
       </c>
       <c r="L26" s="14">
-        <v>19.230769230769</v>
+        <v>23.214285714285</v>
       </c>
       <c r="M26" s="14">
-        <v>31.914893617021</v>
+        <v>30.188679245283</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1415,7 +1415,7 @@
         <v>-60</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1441,22 +1441,22 @@
         <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="15">
         <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L28" s="14">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,14 +1551,14 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
-      </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>0</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>1</v>
@@ -1579,7 +1579,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1613,29 +1613,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14">
+        <v>-100</v>
       </c>
       <c r="I33" s="15">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="15">
+        <v>1</v>
+      </c>
+      <c r="K33" s="14">
+        <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -914,22 +914,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>2</v>
       </c>
       <c r="K15" s="14">
+        <v>50</v>
+      </c>
+      <c r="L15" s="14">
         <v>0</v>
       </c>
-      <c r="L15" s="14">
-        <v>-33.333333333333</v>
-      </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -940,37 +940,37 @@
         <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
         <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I16" s="15">
         <v>17</v>
       </c>
       <c r="J16" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" s="14">
-        <v>-22.727272727272</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="L16" s="14">
-        <v>6.25</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M16" s="14">
-        <v>-45.161290322580</v>
+        <v>-46.875</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.880952380952</v>
+        <v>-90.659340659340</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15">
         <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I17" s="15">
+        <v>40</v>
+      </c>
+      <c r="J17" s="15">
         <v>39</v>
       </c>
-      <c r="J17" s="15">
-        <v>36</v>
-      </c>
       <c r="K17" s="14">
-        <v>8.333333333333</v>
+        <v>2.564102564102</v>
       </c>
       <c r="L17" s="14">
-        <v>105.263157894737</v>
+        <v>90.476190476190</v>
       </c>
       <c r="M17" s="14">
-        <v>225</v>
+        <v>207.692307692308</v>
       </c>
       <c r="N17" s="14">
-        <v>116.666666666667</v>
+        <v>110.526315789474</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
         <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-35.714285714285</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="15">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K18" s="14">
-        <v>-55.319148936170</v>
+        <v>-53.061224489795</v>
       </c>
       <c r="L18" s="14">
-        <v>0</v>
+        <v>4.545454545454</v>
       </c>
       <c r="M18" s="14">
-        <v>-27.586206896551</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.396226415094</v>
+        <v>-93.154761904761</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="F19" s="15">
         <v>45</v>
       </c>
       <c r="G19" s="15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H19" s="14">
-        <v>50</v>
+        <v>60.714285714285</v>
       </c>
       <c r="I19" s="15">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="J19" s="15">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K19" s="14">
-        <v>34.523809523809</v>
+        <v>37.5</v>
       </c>
       <c r="L19" s="14">
-        <v>29.885057471264</v>
+        <v>27.368421052631</v>
       </c>
       <c r="M19" s="14">
-        <v>18.947368421052</v>
+        <v>19.801980198019</v>
       </c>
       <c r="N19" s="14">
-        <v>-46.190476190476</v>
+        <v>-47.161572052401</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="14">
-        <v>-33.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F20" s="15">
         <v>11</v>
       </c>
       <c r="G20" s="15">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-31.25</v>
       </c>
       <c r="I20" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J20" s="15">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K20" s="14">
-        <v>-3.225806451612</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L20" s="14">
-        <v>-9.090909090909</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M20" s="14">
-        <v>3.448275862068</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.163682864450</v>
+        <v>-96.208530805687</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
         <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>17.647058823529</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H21" s="18">
-        <v>12.328767123287</v>
+        <v>5.194805194805</v>
       </c>
       <c r="I21" s="17">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="J21" s="17">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>-1.255230125523</v>
       </c>
       <c r="L21" s="18">
-        <v>24.022346368715</v>
+        <v>20.408163265306</v>
       </c>
       <c r="M21" s="18">
-        <v>13.265306122449</v>
+        <v>14.563106796116</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.180240320427</v>
+        <v>-85.368877867328</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,11 +1185,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -1268,34 +1268,34 @@
         <v>33</v>
       </c>
       <c r="D24" s="15">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E24" s="14">
-        <v>32</v>
+        <v>6.451612903225</v>
       </c>
       <c r="F24" s="15">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="G24" s="15">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="H24" s="14">
-        <v>2.777777777777</v>
+        <v>19.230769230769</v>
       </c>
       <c r="I24" s="15">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="J24" s="15">
-        <v>458</v>
+        <v>489</v>
       </c>
       <c r="K24" s="14">
-        <v>-6.986899563318</v>
+        <v>-6.339468302658</v>
       </c>
       <c r="L24" s="14">
-        <v>11.811023622047</v>
+        <v>12.807881773399</v>
       </c>
       <c r="M24" s="14">
-        <v>107.80487804878</v>
+        <v>101.762114537445</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D25" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E25" s="14">
-        <v>15.789473684210</v>
+        <v>-37.5</v>
       </c>
       <c r="F25" s="15">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G25" s="15">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H25" s="14">
-        <v>-14.655172413793</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I25" s="15">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="J25" s="15">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="K25" s="14">
-        <v>-20.899470899470</v>
+        <v>-22.139303482587</v>
       </c>
       <c r="L25" s="14">
-        <v>-1.644736842105</v>
+        <v>-3.987730061349</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>-12.5</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G26" s="15">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H26" s="14">
-        <v>-24.242424242424</v>
+        <v>-30</v>
       </c>
       <c r="I26" s="15">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J26" s="15">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K26" s="14">
-        <v>-15.853658536585</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L26" s="14">
-        <v>23.214285714285</v>
+        <v>20</v>
       </c>
       <c r="M26" s="14">
-        <v>30.188679245283</v>
+        <v>26.315789473684</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
+        <v>3</v>
+      </c>
+      <c r="G27" s="15">
         <v>2</v>
       </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="14">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I28" s="15">
         <v>10</v>
@@ -1499,8 +1499,8 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="14">
+        <v>-100</v>
       </c>
       <c r="N29" s="13" t="s">
         <v>21</v>
@@ -1540,8 +1540,8 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="14">
+        <v>-100</v>
       </c>
       <c r="N30" s="13" t="s">
         <v>21</v>
@@ -1561,25 +1561,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="15">
+        <v>2</v>
+      </c>
+      <c r="G31" s="15">
         <v>1</v>
       </c>
-      <c r="G31" s="15">
-        <v>3</v>
-      </c>
       <c r="H31" s="14">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I31" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="15">
         <v>6</v>
       </c>
       <c r="K31" s="14">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L31" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1613,11 +1613,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="15">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -332,8 +332,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -549,7 +549,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -567,7 +567,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -857,29 +857,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>-100</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -887,7 +887,7 @@
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -895,40 +895,40 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="15">
-        <v>3</v>
-      </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <v>2</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="15">
         <v>50</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="15">
         <v>0</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="15">
         <v>200</v>
       </c>
     </row>
@@ -936,205 +936,205 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="E16" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="15">
-        <v>2</v>
-      </c>
-      <c r="G16" s="15">
-        <v>7</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-71.428571428571</v>
-      </c>
-      <c r="I16" s="15">
-        <v>17</v>
-      </c>
-      <c r="J16" s="15">
-        <v>23</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-26.086956521739</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-10.526315789473</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-46.875</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-90.659340659340</v>
+      <c r="E16" s="15">
+        <v>100</v>
+      </c>
+      <c r="F16" s="14">
+        <v>3</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I16" s="14">
+        <v>19</v>
+      </c>
+      <c r="J16" s="14">
+        <v>24</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-20.833333333333</v>
+      </c>
+      <c r="L16" s="15">
+        <v>0</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-40.625</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-90.306122448979</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="15">
-        <v>3</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F17" s="15">
-        <v>11</v>
-      </c>
-      <c r="G17" s="15">
-        <v>14</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-21.428571428571</v>
-      </c>
-      <c r="I17" s="15">
-        <v>40</v>
-      </c>
-      <c r="J17" s="15">
-        <v>39</v>
-      </c>
-      <c r="K17" s="14">
-        <v>2.564102564102</v>
-      </c>
-      <c r="L17" s="14">
-        <v>90.476190476190</v>
-      </c>
-      <c r="M17" s="14">
-        <v>207.692307692308</v>
-      </c>
-      <c r="N17" s="14">
-        <v>110.526315789474</v>
+      <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>4</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F17" s="14">
+        <v>13</v>
+      </c>
+      <c r="G17" s="14">
+        <v>13</v>
+      </c>
+      <c r="H17" s="15">
+        <v>0</v>
+      </c>
+      <c r="I17" s="14">
+        <v>42</v>
+      </c>
+      <c r="J17" s="14">
+        <v>43</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-2.325581395348</v>
+      </c>
+      <c r="L17" s="15">
+        <v>68</v>
+      </c>
+      <c r="M17" s="15">
+        <v>200</v>
+      </c>
+      <c r="N17" s="15">
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15">
+      <c r="E18" s="15">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14">
         <v>9</v>
       </c>
-      <c r="G18" s="15">
-        <v>12</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-25</v>
-      </c>
-      <c r="I18" s="15">
-        <v>23</v>
-      </c>
-      <c r="J18" s="15">
-        <v>49</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-53.061224489795</v>
-      </c>
-      <c r="L18" s="14">
-        <v>4.545454545454</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-23.333333333333</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-93.154761904761</v>
+      <c r="G18" s="14">
+        <v>11</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-18.181818181818</v>
+      </c>
+      <c r="I18" s="14">
+        <v>26</v>
+      </c>
+      <c r="J18" s="14">
+        <v>51</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-49.019607843137</v>
+      </c>
+      <c r="L18" s="15">
+        <v>8.333333333333</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-21.212121212121</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-92.737430167597</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>8</v>
-      </c>
-      <c r="D19" s="15">
-        <v>4</v>
-      </c>
-      <c r="E19" s="14">
-        <v>100</v>
-      </c>
-      <c r="F19" s="15">
-        <v>45</v>
-      </c>
-      <c r="G19" s="15">
-        <v>28</v>
-      </c>
-      <c r="H19" s="14">
-        <v>60.714285714285</v>
-      </c>
-      <c r="I19" s="15">
-        <v>121</v>
-      </c>
-      <c r="J19" s="15">
-        <v>88</v>
-      </c>
-      <c r="K19" s="14">
-        <v>37.5</v>
-      </c>
-      <c r="L19" s="14">
-        <v>27.368421052631</v>
-      </c>
-      <c r="M19" s="14">
-        <v>19.801980198019</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-47.161572052401</v>
+      <c r="C19" s="14">
+        <v>7</v>
+      </c>
+      <c r="D19" s="14">
+        <v>11</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-36.363636363636</v>
+      </c>
+      <c r="F19" s="14">
+        <v>37</v>
+      </c>
+      <c r="G19" s="14">
+        <v>33</v>
+      </c>
+      <c r="H19" s="15">
+        <v>12.121212121212</v>
+      </c>
+      <c r="I19" s="14">
+        <v>128</v>
+      </c>
+      <c r="J19" s="14">
+        <v>99</v>
+      </c>
+      <c r="K19" s="15">
+        <v>29.292929292929</v>
+      </c>
+      <c r="L19" s="15">
+        <v>25.490196078431</v>
+      </c>
+      <c r="M19" s="15">
+        <v>19.626168224299</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-48.8</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>2</v>
-      </c>
-      <c r="D20" s="15">
-        <v>7</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-71.428571428571</v>
-      </c>
-      <c r="F20" s="15">
-        <v>11</v>
-      </c>
-      <c r="G20" s="15">
+      <c r="C20" s="14">
+        <v>9</v>
+      </c>
+      <c r="D20" s="14">
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <v>200</v>
+      </c>
+      <c r="F20" s="14">
         <v>16</v>
       </c>
-      <c r="H20" s="14">
-        <v>-31.25</v>
-      </c>
-      <c r="I20" s="15">
-        <v>32</v>
-      </c>
-      <c r="J20" s="15">
-        <v>38</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-15.789473684210</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-11.111111111111</v>
-      </c>
-      <c r="M20" s="14">
-        <v>6.666666666666</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-96.208530805687</v>
+      <c r="G20" s="14">
+        <v>17</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-5.882352941176</v>
+      </c>
+      <c r="I20" s="14">
+        <v>41</v>
+      </c>
+      <c r="J20" s="14">
+        <v>41</v>
+      </c>
+      <c r="K20" s="15">
+        <v>0</v>
+      </c>
+      <c r="L20" s="15">
+        <v>10.810810810810</v>
+      </c>
+      <c r="M20" s="15">
+        <v>28.125</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-95.464601769911</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.647058823529</v>
+        <v>4.545454545454</v>
       </c>
       <c r="F21" s="17">
+        <v>79</v>
+      </c>
+      <c r="G21" s="17">
         <v>81</v>
       </c>
-      <c r="G21" s="17">
-        <v>77</v>
-      </c>
       <c r="H21" s="18">
-        <v>5.194805194805</v>
+        <v>-2.469135802469</v>
       </c>
       <c r="I21" s="17">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="J21" s="17">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.255230125523</v>
+        <v>-0.766283524904</v>
       </c>
       <c r="L21" s="18">
-        <v>20.408163265306</v>
+        <v>23.333333333333</v>
       </c>
       <c r="M21" s="18">
-        <v>14.563106796116</v>
+        <v>18.807339449541</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.368877867328</v>
+        <v>-85.046189376443</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,34 +1185,34 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="15">
-        <v>3</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I22" s="14">
         <v>4</v>
       </c>
-      <c r="J22" s="15">
-        <v>9</v>
-      </c>
-      <c r="K22" s="14">
+      <c r="J22" s="14">
+        <v>10</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-60</v>
+      </c>
+      <c r="L22" s="15">
         <v>-55.555555555555</v>
       </c>
-      <c r="L22" s="14">
-        <v>-55.555555555555</v>
-      </c>
-      <c r="M22" s="14">
+      <c r="M22" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
@@ -1250,7 +1250,7 @@
       <c r="K23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="15">
         <v>-100</v>
       </c>
       <c r="M23" s="13" t="s">
@@ -1264,38 +1264,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>33</v>
-      </c>
-      <c r="D24" s="15">
-        <v>31</v>
-      </c>
-      <c r="E24" s="14">
-        <v>6.451612903225</v>
-      </c>
-      <c r="F24" s="15">
-        <v>155</v>
-      </c>
-      <c r="G24" s="15">
-        <v>130</v>
-      </c>
-      <c r="H24" s="14">
-        <v>19.230769230769</v>
-      </c>
-      <c r="I24" s="15">
-        <v>458</v>
-      </c>
-      <c r="J24" s="15">
-        <v>489</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-6.339468302658</v>
-      </c>
-      <c r="L24" s="14">
-        <v>12.807881773399</v>
-      </c>
-      <c r="M24" s="14">
-        <v>101.762114537445</v>
+      <c r="C24" s="14">
+        <v>29</v>
+      </c>
+      <c r="D24" s="14">
+        <v>35</v>
+      </c>
+      <c r="E24" s="15">
+        <v>-17.142857142857</v>
+      </c>
+      <c r="F24" s="14">
+        <v>131</v>
+      </c>
+      <c r="G24" s="14">
+        <v>128</v>
+      </c>
+      <c r="H24" s="15">
+        <v>2.34375</v>
+      </c>
+      <c r="I24" s="14">
+        <v>486</v>
+      </c>
+      <c r="J24" s="14">
+        <v>524</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-7.251908396946</v>
+      </c>
+      <c r="L24" s="15">
+        <v>11.724137931034</v>
+      </c>
+      <c r="M24" s="15">
+        <v>97.560975609756</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,35 +1305,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>15</v>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="14">
+        <v>19</v>
+      </c>
+      <c r="D25" s="14">
         <v>24</v>
       </c>
-      <c r="E25" s="14">
-        <v>-37.5</v>
-      </c>
-      <c r="F25" s="15">
-        <v>96</v>
-      </c>
-      <c r="G25" s="15">
-        <v>104</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-7.692307692307</v>
-      </c>
-      <c r="I25" s="15">
-        <v>313</v>
-      </c>
-      <c r="J25" s="15">
-        <v>402</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-22.139303482587</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-3.987730061349</v>
+      <c r="E25" s="15">
+        <v>-20.833333333333</v>
+      </c>
+      <c r="F25" s="14">
+        <v>86</v>
+      </c>
+      <c r="G25" s="14">
+        <v>94</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-8.510638297872</v>
+      </c>
+      <c r="I25" s="14">
+        <v>332</v>
+      </c>
+      <c r="J25" s="14">
+        <v>426</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-22.065727699530</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-2.923976608187</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1346,38 +1346,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>3</v>
-      </c>
-      <c r="D26" s="15">
-        <v>2</v>
-      </c>
-      <c r="E26" s="14">
-        <v>50</v>
-      </c>
-      <c r="F26" s="15">
-        <v>21</v>
-      </c>
-      <c r="G26" s="15">
-        <v>30</v>
-      </c>
-      <c r="H26" s="14">
-        <v>-30</v>
-      </c>
-      <c r="I26" s="15">
-        <v>72</v>
-      </c>
-      <c r="J26" s="15">
+      <c r="C26" s="14">
+        <v>7</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="14">
+        <v>24</v>
+      </c>
+      <c r="G26" s="14">
+        <v>18</v>
+      </c>
+      <c r="H26" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="I26" s="14">
+        <v>79</v>
+      </c>
+      <c r="J26" s="14">
         <v>84</v>
       </c>
-      <c r="K26" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="L26" s="14">
-        <v>20</v>
-      </c>
-      <c r="M26" s="14">
-        <v>26.315789473684</v>
+      <c r="K26" s="15">
+        <v>-5.952380952380</v>
+      </c>
+      <c r="L26" s="15">
+        <v>23.4375</v>
+      </c>
+      <c r="M26" s="15">
+        <v>38.596491228070</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,34 +1387,34 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
+      <c r="H27" s="15">
         <v>0</v>
       </c>
-      <c r="F27" s="15">
+      <c r="I27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
-      <c r="H27" s="14">
-        <v>50</v>
-      </c>
-      <c r="I27" s="15">
-        <v>3</v>
-      </c>
-      <c r="J27" s="15">
+      <c r="J27" s="14">
         <v>6</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="15">
         <v>-50</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="15">
         <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>3</v>
-      </c>
-      <c r="G28" s="15">
+      <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="H28" s="14">
-        <v>50</v>
-      </c>
-      <c r="I28" s="15">
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
+        <v>300</v>
+      </c>
+      <c r="I28" s="14">
+        <v>12</v>
+      </c>
+      <c r="J28" s="14">
         <v>10</v>
       </c>
-      <c r="J28" s="15">
-        <v>9</v>
-      </c>
-      <c r="K28" s="14">
-        <v>11.111111111111</v>
-      </c>
-      <c r="L28" s="14">
-        <v>66.666666666666</v>
+      <c r="K28" s="15">
+        <v>20</v>
+      </c>
+      <c r="L28" s="15">
+        <v>71.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1499,7 +1499,7 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="15">
         <v>-100</v>
       </c>
       <c r="N29" s="13" t="s">
@@ -1540,7 +1540,7 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="15">
         <v>-100</v>
       </c>
       <c r="N30" s="13" t="s">
@@ -1551,8 +1551,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>2</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1560,26 +1560,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>2</v>
-      </c>
-      <c r="G31" s="15">
+      <c r="F31" s="14">
+        <v>4</v>
+      </c>
+      <c r="G31" s="14">
         <v>1</v>
       </c>
-      <c r="H31" s="14">
-        <v>100</v>
-      </c>
-      <c r="I31" s="15">
-        <v>5</v>
-      </c>
-      <c r="J31" s="15">
+      <c r="H31" s="15">
+        <v>300</v>
+      </c>
+      <c r="I31" s="14">
+        <v>7</v>
+      </c>
+      <c r="J31" s="14">
         <v>6</v>
       </c>
-      <c r="K31" s="14">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="L31" s="14">
-        <v>66.666666666666</v>
+      <c r="K31" s="15">
+        <v>16.666666666666</v>
+      </c>
+      <c r="L31" s="15">
+        <v>133.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1622,19 +1622,19 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="14">
         <v>1</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="15">
         <v>-100</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="14">
         <v>1</v>
       </c>
-      <c r="K33" s="14">
+      <c r="K33" s="15">
         <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
@@ -1745,31 +1745,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>7</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>5</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>2</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>0</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>2</v>
       </c>
       <c r="K39" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>0</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-60</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-71.428571428571</v>
       </c>
     </row>
@@ -1777,31 +1777,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>9</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>10</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>7</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>3</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>10</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>233.333333333333</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>42.857142857142</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>0</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>11.111111111111</v>
       </c>
     </row>
@@ -1809,31 +1809,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>698</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>659</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>272</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>213</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>75</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-64.788732394366</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-72.426470588235</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-88.619119878603</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-89.255014326647</v>
       </c>
     </row>
@@ -1841,31 +1841,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>137</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>126</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>84</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>98</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>167</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>70.408163265306</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>98.809523809523</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>32.539682539682</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>21.897810218978</v>
       </c>
     </row>
@@ -1873,31 +1873,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>1680</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>1391</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>605</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>350</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>166</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-52.571428571428</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-72.561983471074</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-88.066139468008</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-90.119047619047</v>
       </c>
     </row>
@@ -1905,31 +1905,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>1340</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>1028</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>741</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>668</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>423</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>-36.676646706586</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-42.914979757085</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-58.852140077821</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-68.432835820895</v>
       </c>
     </row>
@@ -1937,31 +1937,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>3477</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>3382</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>925</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>622</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>164</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-73.633440514469</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-82.270270270270</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-95.150798344175</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-95.283290192694</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -857,11 +857,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -895,41 +895,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -940,78 +940,78 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>-20.833333333333</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L16" s="15">
         <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.625</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.306122448979</v>
+        <v>-89.855072463768</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
-        <v>2</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="14">
         <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I17" s="14">
         <v>42</v>
       </c>
       <c r="J17" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.325581395348</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="L17" s="15">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="M17" s="15">
         <v>200</v>
       </c>
       <c r="N17" s="15">
-        <v>100</v>
+        <v>82.608695652173</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J18" s="14">
         <v>51</v>
       </c>
       <c r="K18" s="15">
-        <v>-49.019607843137</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L18" s="15">
-        <v>8.333333333333</v>
+        <v>8</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.212121212121</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.737430167597</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>-36.363636363636</v>
+        <v>350</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="H19" s="15">
-        <v>12.121212121212</v>
+        <v>68.421052631578</v>
       </c>
       <c r="I19" s="14">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="J19" s="14">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K19" s="15">
-        <v>29.292929292929</v>
+        <v>34.653465346534</v>
       </c>
       <c r="L19" s="15">
-        <v>25.490196078431</v>
+        <v>22.522522522522</v>
       </c>
       <c r="M19" s="15">
-        <v>19.626168224299</v>
+        <v>20.353982300885</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.8</v>
+        <v>-50.724637681159</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>-5.882352941176</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I20" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J20" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K20" s="15">
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>10.810810810810</v>
+        <v>20.512820512820</v>
       </c>
       <c r="M20" s="15">
-        <v>28.125</v>
+        <v>42.424242424242</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.464601769911</v>
+        <v>-95.159629248197</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>4.545454545454</v>
+        <v>18.75</v>
       </c>
       <c r="F21" s="17">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.469135802469</v>
+        <v>4.166666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="J21" s="17">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.766283524904</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>23.333333333333</v>
+        <v>22.026431718061</v>
       </c>
       <c r="M21" s="18">
-        <v>18.807339449541</v>
+        <v>19.396551724137</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.046189376443</v>
+        <v>-85.091496232508</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,20 +1185,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1210,7 +1210,7 @@
         <v>-60</v>
       </c>
       <c r="L22" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="M22" s="15">
         <v>-33.333333333333</v>
@@ -1268,34 +1268,34 @@
         <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.142857142857</v>
+        <v>-29.268292682926</v>
       </c>
       <c r="F24" s="14">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G24" s="14">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H24" s="15">
-        <v>2.34375</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="I24" s="14">
-        <v>486</v>
+        <v>515</v>
       </c>
       <c r="J24" s="14">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.251908396946</v>
+        <v>-8.849557522123</v>
       </c>
       <c r="L24" s="15">
-        <v>11.724137931034</v>
+        <v>10.752688172043</v>
       </c>
       <c r="M24" s="15">
-        <v>97.560975609756</v>
+        <v>91.449814126394</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D25" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E25" s="15">
-        <v>-20.833333333333</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="F25" s="14">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G25" s="14">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H25" s="15">
-        <v>-8.510638297872</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="I25" s="14">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="J25" s="14">
-        <v>426</v>
+        <v>457</v>
       </c>
       <c r="K25" s="15">
-        <v>-22.065727699530</v>
+        <v>-22.538293216630</v>
       </c>
       <c r="L25" s="15">
-        <v>-2.923976608187</v>
+        <v>-2.747252747252</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>6</v>
+      </c>
+      <c r="D26" s="14">
         <v>7</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>21</v>
+      <c r="E26" s="15">
+        <v>-14.285714285714</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H26" s="15">
-        <v>33.333333333333</v>
+        <v>35.294117647058</v>
       </c>
       <c r="I26" s="14">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J26" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.952380952380</v>
+        <v>-6.593406593406</v>
       </c>
       <c r="L26" s="15">
-        <v>23.4375</v>
+        <v>23.188405797101</v>
       </c>
       <c r="M26" s="15">
-        <v>38.596491228070</v>
+        <v>39.344262295082</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
         <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,23 +1428,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
         <v>12</v>
@@ -1551,35 +1551,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F31" s="14">
         <v>2</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="14">
-        <v>4</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
+        <v>6</v>
+      </c>
+      <c r="J31" s="14">
         <v>7</v>
       </c>
-      <c r="J31" s="14">
-        <v>6</v>
-      </c>
       <c r="K31" s="15">
-        <v>16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L31" s="15">
-        <v>133.333333333333</v>
+        <v>20</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,14 +895,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-50</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -936,102 +936,102 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14">
+        <v>5</v>
+      </c>
+      <c r="H16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
-        <v>4</v>
-      </c>
-      <c r="G16" s="14">
-        <v>7</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-42.857142857142</v>
-      </c>
       <c r="I16" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>-19.230769230769</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-36.363636363636</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.855072463768</v>
+        <v>-89.908256880733</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>-35.714285714285</v>
+        <v>-68.75</v>
       </c>
       <c r="I17" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.638297872340</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L17" s="15">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="M17" s="15">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="N17" s="15">
-        <v>82.608695652173</v>
+        <v>51.724137931034</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
         <v>0</v>
@@ -1040,19 +1040,19 @@
         <v>27</v>
       </c>
       <c r="J18" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K18" s="15">
-        <v>-47.058823529411</v>
+        <v>-49.056603773584</v>
       </c>
       <c r="L18" s="15">
-        <v>8</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="M18" s="15">
         <v>-30.769230769230</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.857142857142</v>
+        <v>-93.349753694581</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>350</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>68.421052631578</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="J19" s="14">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="K19" s="15">
-        <v>34.653465346534</v>
+        <v>27.927927927927</v>
       </c>
       <c r="L19" s="15">
-        <v>22.522522522522</v>
+        <v>20.338983050847</v>
       </c>
       <c r="M19" s="15">
-        <v>20.353982300885</v>
+        <v>22.413793103448</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.724637681159</v>
+        <v>-52.188552188552</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
         <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>-4.545454545454</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J20" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>4.081632653061</v>
       </c>
       <c r="L20" s="15">
-        <v>20.512820512820</v>
+        <v>24.390243902439</v>
       </c>
       <c r="M20" s="15">
-        <v>42.424242424242</v>
+        <v>41.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.159629248197</v>
+        <v>-95.091434071222</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>18.75</v>
+        <v>-30</v>
       </c>
       <c r="F21" s="17">
+        <v>69</v>
+      </c>
+      <c r="G21" s="17">
         <v>75</v>
       </c>
-      <c r="G21" s="17">
-        <v>72</v>
-      </c>
       <c r="H21" s="18">
-        <v>4.166666666666</v>
+        <v>-8</v>
       </c>
       <c r="I21" s="17">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="J21" s="17">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>-2.356902356902</v>
       </c>
       <c r="L21" s="18">
-        <v>22.026431718061</v>
+        <v>16.465863453815</v>
       </c>
       <c r="M21" s="18">
-        <v>19.396551724137</v>
+        <v>19.341563786008</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.091496232508</v>
+        <v>-85.441767068273</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,17 +1185,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1204,16 +1204,16 @@
         <v>4</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>-60</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="L22" s="15">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D24" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E24" s="15">
-        <v>-29.268292682926</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="F24" s="14">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G24" s="14">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="H24" s="15">
-        <v>-6.060606060606</v>
+        <v>-15.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>515</v>
+        <v>551</v>
       </c>
       <c r="J24" s="14">
-        <v>565</v>
+        <v>608</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.849557522123</v>
+        <v>-9.375</v>
       </c>
       <c r="L24" s="15">
-        <v>10.752688172043</v>
+        <v>11.538461538461</v>
       </c>
       <c r="M24" s="15">
-        <v>91.449814126394</v>
+        <v>98.916967509025</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D25" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E25" s="15">
-        <v>-29.032258064516</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="F25" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G25" s="14">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H25" s="15">
-        <v>-20.408163265306</v>
+        <v>-23.148148148148</v>
       </c>
       <c r="I25" s="14">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="J25" s="14">
-        <v>457</v>
+        <v>486</v>
       </c>
       <c r="K25" s="15">
-        <v>-22.538293216630</v>
+        <v>-21.604938271604</v>
       </c>
       <c r="L25" s="15">
-        <v>-2.747252747252</v>
+        <v>0.793650793650</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-14.285714285714</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G26" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H26" s="15">
-        <v>35.294117647058</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J26" s="14">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.593406593406</v>
+        <v>-3.191489361702</v>
       </c>
       <c r="L26" s="15">
-        <v>23.188405797101</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>39.344262295082</v>
+        <v>40</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,14 +1387,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1415,7 +1415,7 @@
         <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,25 +1438,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>71.428571428571</v>
+        <v>114.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,20 +1554,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
         <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="14">
-        <v>2</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>6</v>
@@ -1622,11 +1622,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -898,79 +898,79 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L15" s="15">
         <v>33.333333333333</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+      <c r="M15" s="15">
+        <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
         <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I16" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.518518518518</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>-8.333333333333</v>
+        <v>-4</v>
       </c>
       <c r="M16" s="15">
-        <v>-38.888888888888</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.908256880733</v>
+        <v>-89.519650655021</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="14">
         <v>5</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>-68.75</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="I17" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J17" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K17" s="15">
-        <v>-15.384615384615</v>
+        <v>-19.642857142857</v>
       </c>
       <c r="L17" s="15">
-        <v>37.5</v>
+        <v>32.352941176470</v>
       </c>
       <c r="M17" s="15">
-        <v>175</v>
+        <v>164.705882352941</v>
       </c>
       <c r="N17" s="15">
-        <v>51.724137931034</v>
+        <v>32.352941176470</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J18" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K18" s="15">
-        <v>-49.056603773584</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="15">
-        <v>-12.903225806451</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M18" s="15">
-        <v>-30.769230769230</v>
+        <v>-28.205128205128</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.349753694581</v>
+        <v>-93.607305936073</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>122.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>11.111111111111</v>
+        <v>34.375</v>
       </c>
       <c r="I19" s="14">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="J19" s="14">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K19" s="15">
-        <v>27.927927927927</v>
+        <v>35</v>
       </c>
       <c r="L19" s="15">
-        <v>20.338983050847</v>
+        <v>24.615384615384</v>
       </c>
       <c r="M19" s="15">
-        <v>22.413793103448</v>
+        <v>35</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.188552188552</v>
+        <v>-47.909967845659</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>16.666666666666</v>
+        <v>61.538461538461</v>
       </c>
       <c r="I20" s="14">
+        <v>53</v>
+      </c>
+      <c r="J20" s="14">
         <v>51</v>
       </c>
-      <c r="J20" s="14">
-        <v>49</v>
-      </c>
       <c r="K20" s="15">
-        <v>4.081632653061</v>
+        <v>3.921568627450</v>
       </c>
       <c r="L20" s="15">
-        <v>24.390243902439</v>
+        <v>15.217391304347</v>
       </c>
       <c r="M20" s="15">
-        <v>41.666666666666</v>
+        <v>43.243243243243</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.091434071222</v>
+        <v>-95.150960658737</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
         <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-30</v>
+        <v>25</v>
       </c>
       <c r="F21" s="17">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H21" s="18">
-        <v>-8</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I21" s="17">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="J21" s="17">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.356902356902</v>
+        <v>-0.315457413249</v>
       </c>
       <c r="L21" s="18">
-        <v>16.465863453815</v>
+        <v>15.328467153284</v>
       </c>
       <c r="M21" s="18">
-        <v>19.341563786008</v>
+        <v>25.896414342629</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.441767068273</v>
+        <v>-85.016595542911</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,11 +1185,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>3</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.279069767441</v>
+        <v>-13.513513513513</v>
       </c>
       <c r="F24" s="14">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G24" s="14">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.333333333333</v>
+        <v>-19.871794871794</v>
       </c>
       <c r="I24" s="14">
-        <v>551</v>
+        <v>582</v>
       </c>
       <c r="J24" s="14">
-        <v>608</v>
+        <v>645</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.375</v>
+        <v>-9.767441860465</v>
       </c>
       <c r="L24" s="15">
-        <v>11.538461538461</v>
+        <v>13.229571984435</v>
       </c>
       <c r="M24" s="15">
-        <v>98.916967509025</v>
+        <v>95.959595959596</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D25" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E25" s="15">
-        <v>-6.896551724137</v>
+        <v>-30</v>
       </c>
       <c r="F25" s="14">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G25" s="14">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.148148148148</v>
+        <v>-21.929824561403</v>
       </c>
       <c r="I25" s="14">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="J25" s="14">
-        <v>486</v>
+        <v>516</v>
       </c>
       <c r="K25" s="15">
-        <v>-21.604938271604</v>
+        <v>-22.093023255814</v>
       </c>
       <c r="L25" s="15">
-        <v>0.793650793650</v>
+        <v>1.772151898734</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G26" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>83.333333333333</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I26" s="14">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="J26" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.191489361702</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="L26" s="15">
-        <v>16.666666666666</v>
+        <v>12.643678160919</v>
       </c>
       <c r="M26" s="15">
-        <v>40</v>
+        <v>44.117647058823</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,29 +1390,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L27" s="15">
         <v>-33.333333333333</v>
@@ -1429,34 +1429,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>50</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L28" s="15">
-        <v>114.285714285714</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1502,8 +1502,8 @@
       <c r="M29" s="15">
         <v>-100</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>21</v>
+      <c r="N29" s="15">
+        <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1543,8 +1543,8 @@
       <c r="M30" s="15">
         <v>-100</v>
       </c>
-      <c r="N30" s="13" t="s">
-        <v>21</v>
+      <c r="N30" s="15">
+        <v>-100</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,26 +1560,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
         <v>7</v>
       </c>
       <c r="K31" s="15">
-        <v>-14.285714285714</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L31" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1628,14 +1628,14 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="14">
-        <v>1</v>
+      <c r="I33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="J33" s="14">
         <v>1</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -866,11 +866,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J16" s="14">
         <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-4</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.135135135135</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.519650655021</v>
+        <v>-88.429752066115</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>-70.588235294117</v>
+        <v>-62.5</v>
       </c>
       <c r="I17" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J17" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K17" s="15">
-        <v>-19.642857142857</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="L17" s="15">
-        <v>32.352941176470</v>
+        <v>37.142857142857</v>
       </c>
       <c r="M17" s="15">
-        <v>164.705882352941</v>
+        <v>152.631578947368</v>
       </c>
       <c r="N17" s="15">
-        <v>32.352941176470</v>
+        <v>29.729729729729</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-28.571428571428</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
         <v>28</v>
       </c>
       <c r="J18" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-52.542372881355</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.222222222222</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="M18" s="15">
-        <v>-28.205128205128</v>
+        <v>-34.883720930232</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.607305936073</v>
+        <v>-94.004282655246</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>122.222222222222</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>34.375</v>
+        <v>69.230769230769</v>
       </c>
       <c r="I19" s="14">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="J19" s="14">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K19" s="15">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="L19" s="15">
-        <v>24.615384615384</v>
+        <v>22.463768115942</v>
       </c>
       <c r="M19" s="15">
-        <v>35</v>
+        <v>36.290322580645</v>
       </c>
       <c r="N19" s="15">
-        <v>-47.909967845659</v>
+        <v>-48.942598187311</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>61.538461538461</v>
+        <v>40</v>
       </c>
       <c r="I20" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J20" s="14">
         <v>51</v>
       </c>
       <c r="K20" s="15">
-        <v>3.921568627450</v>
+        <v>7.843137254901</v>
       </c>
       <c r="L20" s="15">
-        <v>15.217391304347</v>
+        <v>17.021276595744</v>
       </c>
       <c r="M20" s="15">
-        <v>43.243243243243</v>
+        <v>37.5</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.150960658737</v>
+        <v>-95.331069609507</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,48 +1142,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>25</v>
+        <v>36.363636363636</v>
       </c>
       <c r="F21" s="17">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>3.846153846153</v>
+        <v>11.940298507462</v>
       </c>
       <c r="I21" s="17">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="J21" s="17">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.315457413249</v>
+        <v>1.219512195121</v>
       </c>
       <c r="L21" s="18">
-        <v>15.328467153284</v>
+        <v>16.083916083916</v>
       </c>
       <c r="M21" s="18">
-        <v>25.896414342629</v>
+        <v>25.283018867924</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.016595542911</v>
+        <v>-85.303231518371</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1191,29 +1191,29 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>-69.230769230769</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L22" s="15">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
         <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.513513513513</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="F24" s="14">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G24" s="14">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H24" s="15">
-        <v>-19.871794871794</v>
+        <v>-19.620253164557</v>
       </c>
       <c r="I24" s="14">
-        <v>582</v>
+        <v>613</v>
       </c>
       <c r="J24" s="14">
-        <v>645</v>
+        <v>682</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.767441860465</v>
+        <v>-10.117302052785</v>
       </c>
       <c r="L24" s="15">
-        <v>13.229571984435</v>
+        <v>12.683823529411</v>
       </c>
       <c r="M24" s="15">
-        <v>95.959595959596</v>
+        <v>94.603174603174</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>21</v>
       </c>
       <c r="D25" s="14">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-30</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="F25" s="14">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="G25" s="14">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H25" s="15">
-        <v>-21.929824561403</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="I25" s="14">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="J25" s="14">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="K25" s="15">
-        <v>-22.093023255814</v>
+        <v>-21.189591078066</v>
       </c>
       <c r="L25" s="15">
-        <v>1.772151898734</v>
+        <v>2.663438256658</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.5</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G26" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>44.444444444444</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I26" s="14">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J26" s="14">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.921568627450</v>
+        <v>-6.603773584905</v>
       </c>
       <c r="L26" s="15">
-        <v>12.643678160919</v>
+        <v>7.608695652173</v>
       </c>
       <c r="M26" s="15">
-        <v>44.117647058823</v>
+        <v>43.478260869565</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>-55.555555555555</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,25 +1438,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>45.454545454545</v>
+        <v>41.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>112.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-112pct.xlsx
+++ b/data/source/weekly/cs-en-us-112pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -904,14 +904,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
@@ -923,7 +923,7 @@
         <v>-20</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
         <v>300</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I16" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J16" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>3.448275862068</v>
       </c>
       <c r="L16" s="15">
-        <v>7.692307692307</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M16" s="15">
-        <v>-26.315789473684</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.429752066115</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,78 +981,78 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>-62.5</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I17" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J17" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K17" s="15">
-        <v>-18.644067796610</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L17" s="15">
-        <v>37.142857142857</v>
+        <v>38.888888888888</v>
       </c>
       <c r="M17" s="15">
-        <v>152.631578947368</v>
+        <v>163.157894736842</v>
       </c>
       <c r="N17" s="15">
-        <v>29.729729729729</v>
+        <v>11.111111111111</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K18" s="15">
-        <v>-52.542372881355</v>
+        <v>-45.901639344262</v>
       </c>
       <c r="L18" s="15">
-        <v>-24.324324324324</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="M18" s="15">
-        <v>-34.883720930232</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.004282655246</v>
+        <v>-93.223819301848</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>69.230769230769</v>
+        <v>43.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="J19" s="14">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K19" s="15">
-        <v>35.2</v>
+        <v>35.114503816793</v>
       </c>
       <c r="L19" s="15">
-        <v>22.463768115942</v>
+        <v>19.594594594594</v>
       </c>
       <c r="M19" s="15">
-        <v>36.290322580645</v>
+        <v>36.153846153846</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.942598187311</v>
+        <v>-48.093841642228</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>40</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I20" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J20" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K20" s="15">
-        <v>7.843137254901</v>
+        <v>3.703703703703</v>
       </c>
       <c r="L20" s="15">
-        <v>17.021276595744</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M20" s="15">
-        <v>37.5</v>
+        <v>36.585365853658</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.331069609507</v>
+        <v>-95.509222133119</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,75 +1142,75 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>36.363636363636</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>11.940298507462</v>
+        <v>7.246376811594</v>
       </c>
       <c r="I21" s="17">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="J21" s="17">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="K21" s="18">
-        <v>1.219512195121</v>
+        <v>1.156069364161</v>
       </c>
       <c r="L21" s="18">
-        <v>16.083916083916</v>
+        <v>15.894039735099</v>
       </c>
       <c r="M21" s="18">
-        <v>25.283018867924</v>
+        <v>28.205128205128</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.303231518371</v>
+        <v>-85.287936107608</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="14">
         <v>5</v>
       </c>
       <c r="J22" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="L22" s="15">
-        <v>-58.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>-37.5</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.216216216216</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G24" s="14">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="H24" s="15">
-        <v>-19.620253164557</v>
+        <v>-15.032679738562</v>
       </c>
       <c r="I24" s="14">
-        <v>613</v>
+        <v>645</v>
       </c>
       <c r="J24" s="14">
-        <v>682</v>
+        <v>718</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.117302052785</v>
+        <v>-10.167130919220</v>
       </c>
       <c r="L24" s="15">
-        <v>12.683823529411</v>
+        <v>13.356766256590</v>
       </c>
       <c r="M24" s="15">
-        <v>94.603174603174</v>
+        <v>90.828402366863</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1309,31 +1309,31 @@
         <v>21</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E25" s="15">
-        <v>-4.545454545454</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F25" s="14">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G25" s="14">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H25" s="15">
-        <v>-17.857142857142</v>
+        <v>-15.740740740740</v>
       </c>
       <c r="I25" s="14">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="J25" s="14">
-        <v>538</v>
+        <v>565</v>
       </c>
       <c r="K25" s="15">
-        <v>-21.189591078066</v>
+        <v>-21.238938053097</v>
       </c>
       <c r="L25" s="15">
-        <v>2.663438256658</v>
+        <v>4.215456674473</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.090909090909</v>
+        <v>4.761904761904</v>
       </c>
       <c r="I26" s="14">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J26" s="14">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.603773584905</v>
+        <v>-4.464285714285</v>
       </c>
       <c r="L26" s="15">
-        <v>7.608695652173</v>
+        <v>11.458333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>43.478260869565</v>
+        <v>46.575342465753</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,14 +1396,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
@@ -1415,7 +1415,7 @@
         <v>-55.555555555555</v>
       </c>
       <c r="L27" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
         <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>41.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>112.5</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,8 +1551,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>5</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1560,26 +1560,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+      <c r="F31" s="14">
+        <v>5</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J31" s="14">
         <v>7</v>
       </c>
       <c r="K31" s="15">
-        <v>-28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
